--- a/Agent总结的降脂低毒种子化合物表格_校验版.xlsx
+++ b/Agent总结的降脂低毒种子化合物表格_校验版.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026新型低毒降脂化合物筛选比赛_agent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C05B1D74-C565-4066-970A-7D69274A2EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4E40A98-4231-427F-9583-D95C07C04315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="111">
   <si>
     <t>优先级</t>
   </si>
@@ -467,12 +467,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -755,7 +754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23" customWidth="1"/>
@@ -763,7 +762,7 @@
     <col min="4" max="4" width="34.5546875" customWidth="1"/>
     <col min="5" max="5" width="13.33203125" customWidth="1"/>
     <col min="6" max="6" width="30.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.88671875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="24.88671875" style="2" customWidth="1"/>
     <col min="8" max="8" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -786,7 +785,7 @@
       <c r="F1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>57</v>
       </c>
       <c r="H1" t="s">
@@ -812,7 +811,7 @@
       <c r="F2" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="2" t="s">
         <v>58</v>
       </c>
       <c r="H2" t="s">
@@ -838,7 +837,7 @@
       <c r="F3" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>61</v>
       </c>
       <c r="H3" t="s">
@@ -864,7 +863,7 @@
       <c r="F4" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="2" t="s">
         <v>63</v>
       </c>
       <c r="H4" t="s">
@@ -890,7 +889,7 @@
       <c r="F5" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="2" t="s">
         <v>65</v>
       </c>
       <c r="H5" t="s">
@@ -916,7 +915,7 @@
       <c r="F6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="2" t="s">
         <v>70</v>
       </c>
       <c r="H6" t="s">
@@ -942,7 +941,7 @@
       <c r="F7" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="2" t="s">
         <v>72</v>
       </c>
       <c r="H7" t="s">
@@ -968,7 +967,7 @@
       <c r="F8" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="2" t="s">
         <v>82</v>
       </c>
       <c r="H8" t="s">
@@ -994,7 +993,7 @@
       <c r="F9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="2" t="s">
         <v>84</v>
       </c>
       <c r="H9" t="s">
@@ -1020,7 +1019,7 @@
       <c r="F10" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="2" t="s">
         <v>73</v>
       </c>
       <c r="H10" t="s">
@@ -1046,7 +1045,7 @@
       <c r="F11" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H11" t="s">
@@ -1072,7 +1071,7 @@
       <c r="F12" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="2" t="s">
         <v>75</v>
       </c>
       <c r="H12" t="s">
@@ -1098,7 +1097,7 @@
       <c r="F13" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="2" t="s">
         <v>76</v>
       </c>
       <c r="H13" t="s">
@@ -1124,7 +1123,7 @@
       <c r="F14" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="2" t="s">
         <v>77</v>
       </c>
       <c r="H14" t="s">
@@ -1150,7 +1149,7 @@
       <c r="F15" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="2" t="s">
         <v>78</v>
       </c>
       <c r="H15" t="s">
@@ -1176,7 +1175,7 @@
       <c r="F16" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="2" t="s">
         <v>91</v>
       </c>
       <c r="H16" t="s">
@@ -1202,7 +1201,7 @@
       <c r="F17" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="2" t="s">
         <v>79</v>
       </c>
       <c r="H17" t="s">
@@ -1228,7 +1227,7 @@
       <c r="F18" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="2" t="s">
         <v>80</v>
       </c>
       <c r="H18" t="s">
@@ -1254,8 +1253,8 @@
       <c r="F19" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>80</v>
+      <c r="G19" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="H19" t="s">
         <v>29</v>
@@ -1280,8 +1279,8 @@
       <c r="F20" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G20" s="4" t="s">
-        <v>107</v>
+      <c r="G20" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="H20" t="s">
         <v>29</v>
@@ -1306,8 +1305,8 @@
       <c r="F21" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G21" s="4" t="s">
-        <v>108</v>
+      <c r="G21" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="H21" t="s">
         <v>29</v>
@@ -1332,18 +1331,10 @@
       <c r="F22" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G22" s="4" t="s">
-        <v>109</v>
+      <c r="G22" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="H22" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="G23" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="H23" t="s">
         <v>29</v>
       </c>
     </row>
